--- a/proposals/2026-10_pnu-ai-platform/조견표.xlsx
+++ b/proposals/2026-10_pnu-ai-platform/조견표.xlsx
@@ -520,7 +520,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
